--- a/IA_final.xlsx
+++ b/IA_final.xlsx
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>172803.18</v>
+        <v>226017.27</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>304597.18</v>
@@ -1387,61 +1387,61 @@
         <v>369525.15</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>167607.42</v>
+        <v>433598.6900000001</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>603644.62</v>
+        <v>834016.9299999999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>121376.43</v>
+        <v>169161.8</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>110905.7</v>
+        <v>205413.9</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>339728.36</v>
+        <v>416657.41</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>346380.2</v>
+        <v>426604.94</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>193878.04</v>
+        <v>268385.61</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>39215.16</v>
+        <v>123492.33</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0</v>
+        <v>128449.83</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0</v>
+        <v>219804.81</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>0</v>
+        <v>147418.09</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0</v>
+        <v>147596.64</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0</v>
+        <v>99631.49000000001</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0</v>
+        <v>91888.13</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0</v>
+        <v>111970.8</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0</v>
+        <v>491957.67</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0</v>
+        <v>269233.26</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>4103963.46</v>
+        <v>6659603.13</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>3733938.58</v>
+        <v>6230326.51</v>
       </c>
       <c r="Z12" s="2" t="n">
         <v>3336260.9</v>
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>15403551.26</v>
+        <v>52819808.71</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>19620148.19</v>
+        <v>71877268.73999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32455024.15</v>
+        <v>125237116.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>30484407.93</v>
+        <v>124463045.76</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>34393647.14</v>
+        <v>134517050.68</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>36718979.27</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="X18" s="2" t="n">
-        <v>2507661.49</v>
+        <v>72265038.92999999</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>2093463.96</v>
+        <v>60362289.36</v>
       </c>
       <c r="Z18" s="2" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>17913</v>
+        <v>10284.96</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>15991.95</v>
@@ -3104,64 +3104,64 @@
         <v>9748.98</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>631.02</v>
+        <v>-22086.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24338.71</v>
+        <v>39074.08</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>31554.74</v>
+        <v>15969.23</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-14792.7</v>
+        <v>-1258.16</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-3358.73</v>
+        <v>2428.63</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>23929.25</v>
+        <v>20449.12</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-15373.01</v>
+        <v>-934.9099999999999</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2374.92</v>
+        <v>13660.14</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>5567.78</v>
+        <v>20454</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0</v>
+        <v>12545.12</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0</v>
+        <v>15773.88</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>0</v>
+        <v>3586.51</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0</v>
+        <v>3308.76</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0</v>
+        <v>-6452.6</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0</v>
+        <v>-799.89</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0</v>
+        <v>9858.6</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0</v>
+        <v>-25488.02</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0</v>
+        <v>21425.88</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>512560.84</v>
+        <v>683403.8</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>332777.03</v>
+        <v>532694.0800000001</v>
       </c>
       <c r="Z12" s="2" t="n">
         <v>493646.91</v>
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1242008.63</v>
+        <v>4383280.189999999</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1697699.29</v>
+        <v>5660083.13</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2506904.32</v>
+        <v>11130267.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2505541.13</v>
+        <v>11827325.83</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>758738.9</v>
+        <v>5797575.12</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>2466224.67</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="X18" s="2" t="n">
-        <v>-57378.54</v>
+        <v>7801926.55</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>87458.50999999999</v>
+        <v>7645581.81</v>
       </c>
       <c r="Z18" s="2" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.1036612867888195</v>
+        <v>0.04550519524459348</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.05250196341279326</v>
@@ -4761,37 +4761,64 @@
         <v>0.02443361344285081</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.001707651021858729</v>
+        <v>-0.05976995070565562</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.145212604549369</v>
+        <v>0.09011577041434327</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.05227370369009501</v>
+        <v>0.01914736910676382</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0.1218745682337172</v>
+        <v>-0.00743761298354593</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0.030284557060638</v>
+        <v>0.01182310447345579</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.0704364216163761</v>
+        <v>0.04907897833858277</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.04438189596287548</v>
+        <v>-0.002191512362702598</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.0122495564737502</v>
+        <v>0.05089743820467871</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.1419802953755639</v>
+        <v>0.1656297196757078</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0.09766552435297113</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.07176312474690613</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>0.02432883237057271</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0.02241758348970545</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>-0.06476466426428031</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>-0.008705041663161498</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>0.08804616917982189</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>-0.05180937620100527</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>0.07958110376110292</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>0.1248941041984813</v>
+        <v>0.1026192982764125</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>0.08912225599597302</v>
+        <v>0.08550018673098404</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.1479641205518429</v>
@@ -4856,19 +4883,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.08063131735246355</v>
+        <v>0.08298553699930655</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.08652836225086635</v>
+        <v>0.07874649703891907</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.07724241117226222</v>
+        <v>0.08887355310875893</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.08219090676628404</v>
+        <v>0.09502680701552518</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.02206043740902321</v>
+        <v>0.04309918401193421</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.06716484823462794</v>
@@ -5136,10 +5163,10 @@
         </is>
       </c>
       <c r="X18" s="3" t="n">
-        <v>-0.02288129407769467</v>
+        <v>0.1079626699925726</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.04177693605960143</v>
+        <v>0.1266615612340652</v>
       </c>
     </row>
     <row r="19">
